--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M275"/>
+  <dimension ref="A1:M276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1704,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1769,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1895,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2021,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2086,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2212,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2277,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2403,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2468,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2533,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2598,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2663,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2728,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2793,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2980,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3045,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3171,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3236,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3362,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3427,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3492,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3557,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3622,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3748,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3813,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3878,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3943,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4069,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4195,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4260,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4325,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4573,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4638,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4703,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4768,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4833,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4898,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5024,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5150,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5215,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5280,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5467,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5532,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5597,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5662,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5727,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5914,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +5979,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6044,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6109,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6174,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6239,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6304,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6369,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6434,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6499,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6564,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6629,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6694,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6759,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6824,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6889,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6954,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7019,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7084,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7149,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7214,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7340,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7527,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7592,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7779,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7844,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8031,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8157,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8283,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8348,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8413,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8478,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8543,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8608,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8673,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8799,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8864,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8929,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8994,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9059,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9246,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9311,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9437,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9058,7 +9454,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1018-135-CM26</t>
+          <t>5514-66-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9083,27 +9479,27 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,7 +9509,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2658.46</v>
+        <v>75485.50999999999</v>
       </c>
     </row>
     <row r="143">
@@ -9167,7 +9563,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9628,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9241,7 +9645,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5514-66-CM26</t>
+          <t>2322-751-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9261,48 +9665,52 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>75485.50999999999</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2322-751-CM26</t>
+          <t>1018-135-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9322,42 +9730,46 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1134</v>
+        <v>2658.46</v>
       </c>
     </row>
     <row r="147">
@@ -9537,7 +9949,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +10014,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10079,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10144,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10209,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10274,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10339,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10404,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10530,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10656,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10782,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10404,7 +10860,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>642028-62-CM26</t>
+          <t>2343-543-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10429,12 +10885,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10444,28 +10900,32 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2443.02</v>
+        <v>7179.23</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3337-234-CM26</t>
+          <t>1375753-167-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10490,12 +10950,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.101.032-K</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10505,12 +10965,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10520,13 +10980,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1071</v>
+        <v>5497.72</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2343-543-CM26</t>
+          <t>3337-234-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10551,12 +11011,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.101.032-K</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10566,12 +11026,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10581,13 +11041,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7179.23</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1053139-140-CM26</t>
+          <t>642028-62-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10612,43 +11072,47 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2424.03</v>
+        <v>2443.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1375753-167-CM26</t>
+          <t>1725-882-CC26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10673,43 +11137,47 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5497.72</v>
+        <v>94549.84</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4766-3634-CM26</t>
+          <t>728-94-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10734,27 +11202,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>61.211.000-k</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>INSTITUTO NACIONAL DE HIDRAULICA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10764,13 +11232,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1975.4</v>
+        <v>2451.98</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1552-460-CM26</t>
+          <t>4766-3634-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10795,27 +11263,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10825,13 +11293,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>46669.29</v>
+        <v>1975.4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>875-108-CM26</t>
+          <t>1552-460-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10856,32 +11324,32 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10890,13 +11358,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>116524.8</v>
+        <v>46669.29</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>728-94-CM26</t>
+          <t>875-108-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10921,12 +11389,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.211.000-k</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE HIDRAULICA</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10936,28 +11404,32 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2451.98</v>
+        <v>116524.8</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3015-109-CM26</t>
+          <t>1053139-140-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10972,37 +11444,37 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11012,13 +11484,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1804.49</v>
+        <v>2424.03</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2380-1685-CM26</t>
+          <t>3015-109-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11038,48 +11510,52 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1939.94</v>
+        <v>1804.49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2380-1682-CM26</t>
+          <t>2380-1685-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11119,12 +11595,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11134,7 +11610,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>4403.81</v>
+        <v>1939.94</v>
       </c>
     </row>
     <row r="176">
@@ -11188,7 +11664,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11201,7 +11681,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2421-1140-CM26</t>
+          <t>2380-1682-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11221,48 +11701,52 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2705.67</v>
+        <v>4403.81</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1483330-11-CM26</t>
+          <t>2421-1140-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11282,32 +11766,32 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.981.490-8</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11317,13 +11801,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>7540.32</v>
+        <v>2705.67</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>732434-267-CM26</t>
+          <t>1483330-11-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11348,43 +11832,47 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>65.913.720-8</t>
+          <t>61.981.490-8</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>37571.89</v>
+        <v>7540.32</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2380-1681-CM26</t>
+          <t>732434-267-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11409,43 +11897,47 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>65.913.720-8</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7910.05</v>
+        <v>37571.89</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5644-11-CM26</t>
+          <t>2380-1681-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11460,7 +11952,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11470,43 +11962,47 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1545.14</v>
+        <v>7910.05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1173639-88-CM26</t>
+          <t>5644-11-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11531,12 +12027,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>60.511.132-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TALAGANTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11546,28 +12042,32 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3226.89</v>
+        <v>1545.14</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5456-80-CM26</t>
+          <t>1173639-88-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11592,17 +12092,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>60.511.132-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TALAGANTE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11628,7 +12128,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1057532-1518-CM26</t>
+          <t>5456-80-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11653,27 +12153,27 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11683,13 +12183,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>963.54</v>
+        <v>3226.89</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5665-2-CM26</t>
+          <t>1057532-1518-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11714,43 +12214,47 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>902.25</v>
+        <v>963.54</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5562-31-CM26</t>
+          <t>5665-2-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11770,48 +12274,52 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.979.010-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3226.89</v>
+        <v>902.25</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1216090-93-CM26</t>
+          <t>5562-31-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11831,22 +12339,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>71.395.600-7</t>
+          <t>61.979.010-3</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LA MUNICIPALIDAD DE CURICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11866,13 +12374,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1075.63</v>
+        <v>3226.89</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2981-1142-CM26</t>
+          <t>1216090-93-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11892,32 +12400,32 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>71.395.600-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP CULTURAL DE LA MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11927,13 +12435,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>71824.47</v>
+        <v>1075.63</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1589-75-CM26</t>
+          <t>2981-1142-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11953,48 +12461,52 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3152.31</v>
+        <v>71824.47</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2378-318-CM26</t>
+          <t>1589-75-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12019,43 +12531,47 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1134</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2378-317-CM26</t>
+          <t>2378-318-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12095,28 +12611,32 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1004.99</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2626-456-CM26</t>
+          <t>2378-317-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12136,48 +12656,52 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2373.01</v>
+        <v>1004.99</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4359-186-CM26</t>
+          <t>2626-456-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12197,22 +12721,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12225,20 +12749,24 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>736.37</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1343-136-CM26</t>
+          <t>4359-186-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12263,43 +12791,47 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>60.511.042-8</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3152.31</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>878-30-CM26</t>
+          <t>1343-136-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12314,7 +12846,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12324,17 +12856,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.511.050-9</t>
+          <t>60.511.042-8</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE VALPARAÍSO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12347,20 +12879,24 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2101.54</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1426394-112-CM26</t>
+          <t>878-30-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12385,43 +12921,47 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.511.050-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE VALPARAÍSO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>43363.6</v>
+        <v>2101.54</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1426397-244-CM26</t>
+          <t>1426394-112-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12476,13 +13016,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>31438.61</v>
+        <v>43363.6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1390255-20-CM26</t>
+          <t>2328-1311-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12502,48 +13042,52 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>814.34</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2859-1047-CM26</t>
+          <t>1426397-244-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12563,32 +13107,32 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12598,13 +13142,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6328.04</v>
+        <v>31438.61</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1432083-2320-CM26</t>
+          <t>2859-1047-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12624,48 +13168,52 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2019.87</v>
+        <v>6328.04</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1078634-14-CM26</t>
+          <t>1432083-2320-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12690,12 +13238,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12705,28 +13253,32 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3152.31</v>
+        <v>2019.87</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1707-38-CM26</t>
+          <t>1078634-14-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12751,17 +13303,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12774,7 +13326,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12787,7 +13343,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2328-1311-CM26</t>
+          <t>1707-38-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12812,17 +13368,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12835,7 +13391,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12848,7 +13408,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>752-267-CM26</t>
+          <t>1390255-20-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12868,48 +13428,52 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>9979.26</v>
+        <v>814.34</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5603-136-CM26</t>
+          <t>752-267-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12929,48 +13493,52 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5633.75</v>
+        <v>9979.26</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>889473-1658-CM26</t>
+          <t>5603-136-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12995,43 +13563,47 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4019.96</v>
+        <v>5633.75</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1271357-123-CM26</t>
+          <t>889473-1658-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13051,22 +13623,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13079,20 +13651,24 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>21646.1</v>
+        <v>4019.96</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3714-278-CM26</t>
+          <t>1271357-123-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13117,43 +13693,47 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>18798.54</v>
+        <v>21646.1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1577-185-CM26</t>
+          <t>3714-278-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13178,27 +13758,27 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>60.511.100-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13208,13 +13788,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3152.31</v>
+        <v>18798.54</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1076403-39-CM26</t>
+          <t>1577-185-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13234,48 +13814,52 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.511.100-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>18000.06</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>752-268-CM26</t>
+          <t>1076403-39-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13295,32 +13879,32 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13330,13 +13914,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2391.77</v>
+        <v>18000.06</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5178-4194-CM26</t>
+          <t>752-268-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13351,37 +13935,37 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13391,13 +13975,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>758.03</v>
+        <v>2391.77</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2981-1184-CM26</t>
+          <t>5178-4194-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13417,17 +14001,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13437,12 +14021,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13452,13 +14036,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>57643.6</v>
+        <v>758.03</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1183926-184-CM26</t>
+          <t>2981-1184-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13483,43 +14067,47 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>65.199.122-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL LIBERTADOR GENERA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5974.23</v>
+        <v>57643.6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1562-429-CM26</t>
+          <t>1183926-184-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13539,48 +14127,52 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>65.199.122-6</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL LIBERTADOR GENERA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>19753.95</v>
+        <v>5974.23</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2766-581-CM26</t>
+          <t>1562-429-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13600,17 +14192,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13620,28 +14212,32 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>901.89</v>
+        <v>19753.95</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1483330-14-CM26</t>
+          <t>2766-581-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13666,12 +14262,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.981.490-8</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13681,12 +14277,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13696,13 +14292,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>37687.07</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4314-410-CM26</t>
+          <t>1483330-14-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13722,48 +14318,52 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>61.981.490-8</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1141.67</v>
+        <v>37687.07</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2932-116-CM26</t>
+          <t>4314-410-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13783,48 +14383,52 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.511.054-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN ANTONIO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2101.54</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1271357-124-CM26</t>
+          <t>2932-116-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13849,43 +14453,47 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>60.511.054-1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1570.56</v>
+        <v>2101.54</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1271357-122-CM26</t>
+          <t>1271357-124-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13905,7 +14513,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13925,12 +14533,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13940,13 +14548,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8701.049999999999</v>
+        <v>1570.56</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5441-474-CM26</t>
+          <t>1271357-122-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13966,17 +14574,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13986,28 +14594,32 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>901.89</v>
+        <v>8701.049999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1588-191-CM26</t>
+          <t>5441-474-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14027,17 +14639,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14047,12 +14659,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14062,13 +14674,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>16344.3</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2981-1176-CM26</t>
+          <t>1588-191-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14088,17 +14700,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14108,28 +14720,32 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>70380.17</v>
+        <v>16344.3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2343-557-CM26</t>
+          <t>2981-1176-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14144,7 +14760,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14154,12 +14770,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14169,28 +14785,32 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>456.96</v>
+        <v>70380.17</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2345-364-CM26</t>
+          <t>2343-557-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14215,12 +14835,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14230,32 +14850,28 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>136572.73</v>
+        <v>456.96</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5061-661-CM26</t>
+          <t>2345-364-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14280,43 +14896,47 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1705.92</v>
+        <v>136572.73</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2341-492-CM26</t>
+          <t>5061-661-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14341,43 +14961,47 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3749.99</v>
+        <v>1705.92</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>867990-568-CM26</t>
+          <t>2341-492-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14402,12 +15026,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14417,12 +15041,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14432,13 +15056,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6008.31</v>
+        <v>3749.99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1422039-254-CM26</t>
+          <t>867990-568-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14463,12 +15087,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>65.125.012-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO TERRITORIAL Y TURISMO DE LA REGION METROPOLITANA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14478,12 +15102,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.086.318-1</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14493,13 +15117,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>280.84</v>
+        <v>6008.31</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2783-866-CM26</t>
+          <t>1422039-254-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14524,43 +15148,47 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>65.125.012-9</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>CORPORACION DE DESARROLLO TERRITORIAL Y TURISMO DE LA REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>469.55</v>
+        <v>280.84</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1551737-8-CM26</t>
+          <t>2783-866-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14585,43 +15213,47 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>65.281.096-9</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE DESAROLLO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>6348.65</v>
+        <v>469.55</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1107282-223-CM26</t>
+          <t>1551737-8-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14636,7 +15268,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14646,43 +15278,47 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>65.281.096-9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>CORPORACIÓN DE DESAROLLO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr"/>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>901.89</v>
+        <v>6348.65</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2428-1064-CM26</t>
+          <t>1107282-223-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14702,22 +15338,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14743,7 +15379,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5178-4216-CM26</t>
+          <t>2428-1064-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14763,32 +15399,32 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14798,13 +15434,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3603.32</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1107282-225-CM26</t>
+          <t>5178-4216-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14829,43 +15465,47 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1050.76</v>
+        <v>3603.32</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1214102-2041-CM26</t>
+          <t>1107282-225-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14890,17 +15530,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14920,13 +15560,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>901.89</v>
+        <v>1050.76</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2981-1183-CM26</t>
+          <t>1214102-2041-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14951,12 +15591,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14966,12 +15606,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14981,13 +15621,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1583.81</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2770-318-CM26</t>
+          <t>2981-1183-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15012,12 +15652,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15027,12 +15667,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15042,13 +15682,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>18413.17</v>
+        <v>1583.81</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2756-212-CM26</t>
+          <t>2770-318-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15073,43 +15713,47 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>26271.87</v>
+        <v>18413.17</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>867990-587-CM26</t>
+          <t>2756-212-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15124,7 +15768,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15134,27 +15778,27 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15164,13 +15808,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>73577.11</v>
+        <v>26271.87</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2852-1027-CM26</t>
+          <t>867990-587-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15195,43 +15839,47 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8975.99</v>
+        <v>73577.11</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5586-3394-CM26</t>
+          <t>2852-1027-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15256,43 +15904,47 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2903.6</v>
+        <v>8975.99</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3383-143-CM26</t>
+          <t>5586-3394-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15312,32 +15964,32 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.101.031-1</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15347,13 +15999,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8310.959999999999</v>
+        <v>2903.6</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>867990-582-CM26</t>
+          <t>3383-143-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15373,17 +16025,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.101.031-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15393,12 +16045,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15408,13 +16060,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>73627.67999999999</v>
+        <v>8310.959999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1053139-145-CM26</t>
+          <t>867990-582-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15439,43 +16091,47 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1915.78</v>
+        <v>73627.67999999999</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1232565-309-CM26</t>
+          <t>1053139-145-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15500,43 +16156,47 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>6253.94</v>
+        <v>1915.78</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2703-811-CM26</t>
+          <t>1232565-309-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15556,48 +16216,52 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4511.23</v>
+        <v>6253.94</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1483311-9-CM26</t>
+          <t>2703-811-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15617,17 +16281,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15637,28 +16301,32 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3938.92</v>
+        <v>4511.23</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1483311-8-CM26</t>
+          <t>1483311-9-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15698,12 +16366,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15713,13 +16381,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>21539</v>
+        <v>3938.92</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1214102-2052-CM26</t>
+          <t>1483311-8-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15744,12 +16412,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15759,28 +16427,32 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>901.89</v>
+        <v>21539</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4766-3641-CM26</t>
+          <t>1214102-2052-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15800,32 +16472,32 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15835,13 +16507,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1005.54</v>
+        <v>901.89</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1431841-1146-CM26</t>
+          <t>4766-3641-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15861,32 +16533,32 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15896,13 +16568,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>35160.93</v>
+        <v>1005.54</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1359575-208-CM26</t>
+          <t>1431841-1146-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15927,43 +16599,47 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>11144.11</v>
+        <v>35160.93</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1393093-793-CM26</t>
+          <t>1359575-208-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15988,43 +16664,47 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>30392.01</v>
+        <v>11144.11</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5441-486-CM26</t>
+          <t>1393093-793-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16039,7 +16719,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16049,43 +16729,47 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>997.78</v>
+        <v>30392.01</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1501718-60-CM26</t>
+          <t>5441-486-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16110,12 +16794,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16125,12 +16809,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16140,13 +16824,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>9639</v>
+        <v>997.78</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>867990-598-CM26</t>
+          <t>1501718-60-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16166,17 +16850,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16186,28 +16870,32 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1141.67</v>
+        <v>9639</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1217466-119-CM26</t>
+          <t>867990-598-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16227,17 +16915,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.905.003-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16247,28 +16935,32 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>900.83</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1217466-117-CM26</t>
+          <t>1217466-119-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16308,28 +17000,32 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1141.67</v>
+        <v>900.83</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2012-41-CM26</t>
+          <t>1217466-117-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16354,43 +17050,47 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.955.300-4</t>
+          <t>60.905.003-9</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PALENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3213</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5585-74-CM26</t>
+          <t>2012-41-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16415,43 +17115,47 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.955.300-4</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PALENA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1141.67</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3674-597-CM26</t>
+          <t>5585-74-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16476,43 +17180,47 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>277.59</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>564953-1010-CM26</t>
+          <t>3674-597-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16537,43 +17245,47 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2023</v>
+        <v>277.59</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1375758-89-CM26</t>
+          <t>564953-1010-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16598,12 +17310,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16613,28 +17325,32 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5012.26</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1375758-88-CM26</t>
+          <t>1375758-89-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16674,12 +17390,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16689,13 +17405,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>24333.23</v>
+        <v>5012.26</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1298355-819-CM26</t>
+          <t>1375758-88-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16720,12 +17436,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16735,28 +17451,32 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1801.66</v>
+        <v>24333.23</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3177-336-CM26</t>
+          <t>1298355-819-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16771,7 +17491,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -16781,43 +17501,47 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>10013.85</v>
+        <v>1801.66</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1145-168-CM26</t>
+          <t>3177-336-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16842,43 +17566,47 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>37800.49</v>
+        <v>10013.85</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1145-169-CM26</t>
+          <t>1145-168-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16918,28 +17646,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>33114.92</v>
+        <v>37800.49</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>369-309-CM26</t>
+          <t>1145-169-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16964,27 +17696,27 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>60.511.043-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHOAPA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16994,13 +17726,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2142</v>
+        <v>33114.92</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5178-4282-CM26</t>
+          <t>369-309-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17025,43 +17757,47 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.511.043-6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHOAPA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2344.3</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>542343-94-CM26</t>
+          <t>5178-4282-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17101,28 +17837,32 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>21208.66</v>
+        <v>2344.3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1298355-822-CM26</t>
+          <t>542343-94-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17147,12 +17887,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17162,82 +17902,155 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2019.87</v>
+        <v>21208.66</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
+          <t>1298355-822-CM26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>71.293.900-1</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>2019.87</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
           <t>1013353-113-CM26</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
         <is>
           <t>65.154.021-6</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G276" t="inlineStr">
         <is>
           <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr">
+      <c r="J276" t="inlineStr">
         <is>
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M275" s="2" t="n">
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="n">
         <v>15541.78</v>
       </c>
     </row>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2026.xlsx
@@ -6345,7 +6345,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
